--- a/test-data/TestData.xlsx
+++ b/test-data/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mponlinegov-my.sharepoint.com/personal/shailendra_tale_mponline_gov_in/Documents/Desktop/Automation/Playwright_Framework1/test-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="745" documentId="13_ncr:1_{7E1CB7C1-E4AF-4550-B45B-D50296C0774A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBFD69C0-6F2B-4BB2-A247-F1D977A0EC8E}"/>
+  <xr:revisionPtr revIDLastSave="748" documentId="13_ncr:1_{7E1CB7C1-E4AF-4550-B45B-D50296C0774A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92E2F04B-FD2F-4903-960A-842921E8DA4F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3232,7 +3232,7 @@
     </row>
     <row r="3" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>496</v>
@@ -3461,7 +3461,7 @@
     </row>
     <row r="4" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>497</v>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="5" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>498</v>
@@ -3923,7 +3923,7 @@
     </row>
     <row r="6" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>499</v>
@@ -4156,7 +4156,7 @@
     </row>
     <row r="7" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>500</v>
@@ -4399,7 +4399,7 @@
     </row>
     <row r="8" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>501</v>
@@ -4626,7 +4626,7 @@
     </row>
     <row r="9" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>502</v>
@@ -4863,7 +4863,7 @@
     </row>
     <row r="10" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>503</v>
@@ -5102,7 +5102,7 @@
     </row>
     <row r="11" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>504</v>
@@ -5341,7 +5341,7 @@
     </row>
     <row r="12" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>505</v>
@@ -5582,7 +5582,7 @@
     </row>
     <row r="13" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>506</v>
@@ -5833,7 +5833,7 @@
     </row>
     <row r="14" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>507</v>
@@ -6060,7 +6060,7 @@
     </row>
     <row r="15" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>508</v>
@@ -6297,7 +6297,7 @@
     </row>
     <row r="16" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>509</v>
@@ -6536,7 +6536,7 @@
     </row>
     <row r="17" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>510</v>
@@ -6775,7 +6775,7 @@
     </row>
     <row r="18" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>511</v>
@@ -7016,7 +7016,7 @@
     </row>
     <row r="19" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>512</v>
@@ -7267,7 +7267,7 @@
     </row>
     <row r="20" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>513</v>
@@ -7488,7 +7488,7 @@
     </row>
     <row r="21" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>514</v>
@@ -7719,7 +7719,7 @@
     </row>
     <row r="22" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>515</v>
@@ -7952,7 +7952,7 @@
     </row>
     <row r="23" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>516</v>
@@ -8185,7 +8185,7 @@
     </row>
     <row r="24" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>517</v>
@@ -8420,7 +8420,7 @@
     </row>
     <row r="25" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>518</v>
@@ -13044,7 +13044,7 @@
     </row>
     <row r="2" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>462</v>
@@ -13228,7 +13228,7 @@
     </row>
     <row r="3" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>463</v>
@@ -13422,7 +13422,7 @@
     </row>
     <row r="4" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>464</v>
@@ -13618,7 +13618,7 @@
     </row>
     <row r="5" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>465</v>
@@ -13810,7 +13810,7 @@
     </row>
     <row r="6" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>466</v>
@@ -14004,7 +14004,7 @@
     </row>
     <row r="7" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>467</v>
@@ -14400,7 +14400,7 @@
     </row>
     <row r="9" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>469</v>
@@ -14602,7 +14602,7 @@
     </row>
     <row r="10" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>470</v>
@@ -14806,7 +14806,7 @@
     </row>
     <row r="11" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>471</v>
@@ -15006,7 +15006,7 @@
     </row>
     <row r="12" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>472</v>
@@ -15208,7 +15208,7 @@
     </row>
     <row r="13" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>473</v>
@@ -15420,7 +15420,7 @@
     </row>
     <row r="14" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>474</v>
@@ -15612,7 +15612,7 @@
     </row>
     <row r="15" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>475</v>
@@ -15814,7 +15814,7 @@
     </row>
     <row r="16" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>476</v>
@@ -16018,7 +16018,7 @@
     </row>
     <row r="17" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>477</v>
@@ -16218,7 +16218,7 @@
     </row>
     <row r="18" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>478</v>
@@ -16420,7 +16420,7 @@
     </row>
     <row r="19" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>479</v>
@@ -16632,7 +16632,7 @@
     </row>
     <row r="20" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>480</v>
@@ -16818,7 +16818,7 @@
     </row>
     <row r="21" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>481</v>
@@ -17014,7 +17014,7 @@
     </row>
     <row r="22" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>482</v>
@@ -17212,7 +17212,7 @@
     </row>
     <row r="23" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>483</v>
@@ -17406,7 +17406,7 @@
     </row>
     <row r="24" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>484</v>
@@ -17602,7 +17602,7 @@
     </row>
     <row r="25" spans="1:72" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>485</v>
